--- a/R_sediment_traps/tables/env_table_v2.xlsx
+++ b/R_sediment_traps/tables/env_table_v2.xlsx
@@ -1,30 +1,180 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deniseong/Documents/GitHub/TAN1810_sedtraps/R_sediment_traps/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53130674-D473-6C46-9677-23B637E6C091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="16420" yWindow="780" windowWidth="17780" windowHeight="19940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="49">
+  <si>
+    <t>cycle_name</t>
+  </si>
+  <si>
+    <t>SA1-a</t>
+  </si>
+  <si>
+    <t>SA1-b</t>
+  </si>
+  <si>
+    <t>SA2</t>
+  </si>
+  <si>
+    <t>ST1</t>
+  </si>
+  <si>
+    <t>ST2</t>
+  </si>
+  <si>
+    <t>s_mean</t>
+  </si>
+  <si>
+    <t>34.58 ± 0.02</t>
+  </si>
+  <si>
+    <t>34.61 ± 0</t>
+  </si>
+  <si>
+    <t>34.37 ± 0.01</t>
+  </si>
+  <si>
+    <t>34.36 ± 0</t>
+  </si>
+  <si>
+    <t>34.98 ± 0.01</t>
+  </si>
+  <si>
+    <t>34.75 ± 0.02</t>
+  </si>
+  <si>
+    <t>t_mean</t>
+  </si>
+  <si>
+    <t>10.74 ± 0.18</t>
+  </si>
+  <si>
+    <t>11.35 ± 0.05</t>
+  </si>
+  <si>
+    <t>10.2 ± 0.07</t>
+  </si>
+  <si>
+    <t>11.4 ± 0.02</t>
+  </si>
+  <si>
+    <t>13.38 ± 0.07</t>
+  </si>
+  <si>
+    <t>12.99 ± 0.41</t>
+  </si>
+  <si>
+    <t>NO3_um</t>
+  </si>
+  <si>
+    <t>2.12 ± 0.39</t>
+  </si>
+  <si>
+    <t>1.91 ± 0.49</t>
+  </si>
+  <si>
+    <t>2.42 ± 0.19</t>
+  </si>
+  <si>
+    <t>2.3 ± 0.13</t>
+  </si>
+  <si>
+    <t>0.57 ± 0.23</t>
+  </si>
+  <si>
+    <t>0.79 ± 0.15</t>
+  </si>
+  <si>
+    <t>npp_int</t>
+  </si>
+  <si>
+    <t>638.2 ± 235.6</t>
+  </si>
+  <si>
+    <t>389.9 ± 5.3</t>
+  </si>
+  <si>
+    <t>321.4 ± 62.2</t>
+  </si>
+  <si>
+    <t>228.5 ± 40.5</t>
+  </si>
+  <si>
+    <t>755.5 ± 371.5</t>
+  </si>
+  <si>
+    <t>452.3 ± 102.1</t>
+  </si>
+  <si>
+    <t>chl_int</t>
+  </si>
+  <si>
+    <t>65.2 ± 12.3</t>
+  </si>
+  <si>
+    <t>45.6 ± 7</t>
+  </si>
+  <si>
+    <t>31 ± 7.6</t>
+  </si>
+  <si>
+    <t>7.9 ± 1.2</t>
+  </si>
+  <si>
+    <t>70.7 ± 18.5</t>
+  </si>
+  <si>
+    <t>32.1 ± 4</t>
+  </si>
+  <si>
+    <t>Deployment dates</t>
+  </si>
+  <si>
+    <t>24-28 Oct 2018</t>
+  </si>
+  <si>
+    <t>2-6 Nov 2018</t>
+  </si>
+  <si>
+    <t>7-10 Nov 2018</t>
+  </si>
+  <si>
+    <t>12-15 Nov2018</t>
+  </si>
+  <si>
+    <t>16-19 Nov 2018</t>
+  </si>
+  <si>
+    <t>Duration (Days)</t>
+  </si>
+  <si>
+    <t>SA1</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -52,24 +202,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +262,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +296,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +331,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,267 +507,371 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>var</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>X1</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>X2</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>X3</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>X4</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>X5</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>X6</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>cycle_name</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SA1-a</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SA1-b</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SA2</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>SA3</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ST1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ST2</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>s_mean</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>34.58 ± 0.02</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>34.61 ± 0</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>34.37 ± 0.01</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>34.36 ± 0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>34.98 ± 0.01</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>34.75 ± 0.02</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>t_mean</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>10.74 ± 0.18</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>11.35 ± 0.05</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>10.2 ± 0.07</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>11.4 ± 0.02</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>13.38 ± 0.07</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>12.99 ± 0.41</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NO3_um</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2.12 ± 0.39</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1.91 ± 0.49</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2.42 ± 0.19</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2.3 ± 0.13</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.57 ± 0.23</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.79 ± 0.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>npp_int</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>638.2 ± 235.6</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>389.9 ± 5.3</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>321.4 ± 62.2</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>228.5 ± 40.5</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>755.5 ± 371.5</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>452.3 ± 102.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>chl_int</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>65.2 ± 12.3</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>45.6 ± 7</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>31 ± 7.6</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>7.9 ± 1.2</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>70.7 ± 18.5</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>32.1 ± 4</t>
-        </is>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8">
+        <v>3.43</v>
+      </c>
+      <c r="D8">
+        <v>4.07</v>
+      </c>
+      <c r="E8">
+        <v>2.89</v>
+      </c>
+      <c r="F8">
+        <v>2.96</v>
+      </c>
+      <c r="G8">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15">
+        <v>4.07</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18">
+        <v>2.93</v>
       </c>
     </row>
   </sheetData>
